--- a/tests/fixtures/banks/nh_sample.xlsx
+++ b/tests/fixtures/banks/nh_sample.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="거래내역" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet0" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -419,357 +419,328 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>농협은행 거래명세표</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>계좌번호: 302-1234-5678-01</t>
-        </is>
-      </c>
-    </row>
+          <t>입출금거래내역조회 결과</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>예금주: 주식회사 에이티링크</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>조회기간: 2026.01.01 ~ 2026.01.31</t>
-        </is>
-      </c>
-    </row>
+          <t>현재시간 : 2026/05/07 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>계좌번호</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>301-0330-2822-11</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>조회일</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026/01/01 ~ 2026/01/31</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>현재잔액: 12,345,678 원</t>
+          <t>예금주명</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>(주)에이티링크</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>예금종류</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>보통예금</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>※ 거래내역은 최근 1년 이내 데이터입니다</t>
-        </is>
-      </c>
-    </row>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>현재통장잔액</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>15,925원</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>거래일자</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>출금금액(원)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>입금금액(원)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>거래 후 잔액(원)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>거래내용</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>거래기록사항</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>거래점</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>거래시간</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>거래내용</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>출금금액</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>입금금액</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>잔액</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>거래구분</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>상대계좌</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>상대은행</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>메모</t>
+          <t>이체메모</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
+      <c r="A11" t="n">
+        <v>1</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>2026/01/01</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3200000</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>600000000</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>G-기업은행</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1월급여</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>농협 000016</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>10:01:00</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>급여이체</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>3200000</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>12000000</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>이체</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>333-444</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>국민은행</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>임직원A</t>
-        </is>
-      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-01-02</t>
-        </is>
+      <c r="A12" t="n">
+        <v>2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>2026/01/02</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>150000</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>600000000</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>G-기업은행</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>보험료</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>농협 000016</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>10:02:00</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>접대비거래처식사</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>150000</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>12000000</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>이체</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>333-444</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>국민은행</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>한정식집</t>
-        </is>
-      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-01-03</t>
-        </is>
+      <c r="A13" t="n">
+        <v>3</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>2026/01/03</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>600000000</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>인터넷당행</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>사무실임대료</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>농협 000016</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>10:03:00</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>도서구입</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>45000</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>12000000</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>이체</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>333-444</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>국민은행</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-01-04</t>
-        </is>
+      <c r="A14" t="n">
+        <v>4</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>2026/01/04</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>320000</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>600000000</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>G-국민은행</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>근로소득세</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>농협 000016</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>10:04:00</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>단기차입금상환</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>12000000</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>이체</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>333-444</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>국민은행</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>국민은행</t>
-        </is>
-      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-01-05</t>
-        </is>
+      <c r="A15" t="n">
+        <v>5</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>2026/01/05</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>50000</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>600000000</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>알수없음</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>모르는거래</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>농협 000016</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>10:05:00</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>알수없음ABC</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>7000</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>12000000</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>이체</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>333-444</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>국민은행</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
